--- a/nilai-nilai/gti-2026/GTI_PAIK6404_2025_2_A.xlsx
+++ b/nilai-nilai/gti-2026/GTI_PAIK6404_2025_2_A.xlsx
@@ -34,7 +34,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -51,6 +51,11 @@
         <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD7BE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -64,7 +69,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -76,6 +81,10 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="3" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -616,7 +625,7 @@
       </c>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="n"/>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="6" t="n">
         <v>60</v>
       </c>
       <c r="H8" s="3" t="n"/>
@@ -658,7 +667,7 @@
       </c>
       <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="n"/>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="6" t="n">
         <v>60</v>
       </c>
       <c r="H9" s="3" t="n"/>
@@ -701,7 +710,7 @@
       <c r="E10" s="3" t="n"/>
       <c r="F10" s="3" t="n"/>
       <c r="G10" s="5" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H10" s="3" t="n"/>
       <c r="I10" s="3" t="n">
